--- a/stories/arbres/ATOM-SEC.MAI.002-01.xlsx
+++ b/stories/arbres/ATOM-SEC.MAI.002-01.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -602,7 +602,6 @@
           <t>secondary_lessons</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -819,6 +818,18 @@
       <c r="B29" t="inlineStr">
         <is>
           <t>xlsx-arbre-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>voice_cast</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>voix-roles-v1</t>
         </is>
       </c>
     </row>
@@ -833,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV6"/>
+  <dimension ref="A1:AW6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1127,6 +1138,11 @@
           <t>notes</t>
         </is>
       </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>script</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1151,7 +1167,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Hugo est dans la cuisine. Papa coupe des poires. Un petit pot fermé est sur la table. Hugo ne le connaît pas. C'est de l'inconnu. Hugo a envie de goûter. Il va vers papa. Hugo dit : papa, je peux. Avant de goûter l'inconnu, il faut demander. Hugo va demander à l'adulte. Papa prend le pot. Papa dit : c'est de la compote. Tu peux goûter. Hugo goûte une petite cuillère. C'est doux. Papa dit : on demande à un adulte. Parce que Hugo a demandé, papa a dit oui. Hugo range la cuillère. Il sourit.</t>
+          <t>Hugo est dans la cuisine. Papa coupe des poires. Un petit pot fermé est sur la table. Hugo ne le connaît pas. C'est de l'inconnu. Hugo a envie de goûter. Il va vers papa. Papa, je peux. Avant de goûter l'inconnu, il faut demander. Hugo va demander à l'adulte. Papa prend le pot. C'est de la compote. Tu peux goûter. Hugo goûte une petite cuillère. C'est doux. On demande à un adulte. Parce que Hugo a demandé, papa a dit oui. Hugo range la cuillère. Il sourit.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1289,6 +1305,17 @@
         <v>8</v>
       </c>
       <c r="AV2" s="2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>narrateur|Hugo est dans la cuisine. Papa coupe des poires. Un petit pot fermé est sur la table. Hugo ne le connaît pas. C'est de l'inconnu. Hugo a envie de goûter. Il va vers papa.
+enfant-m|Papa, je peux. Avant de goûter l'inconnu, il faut demander.
+narrateur|Hugo va demander à l'adulte. Papa prend le pot.
+papa|C'est de la compote. Tu peux goûter.
+narrateur|Hugo goûte une petite cuillère. C'est doux.
+papa|On demande à un adulte. Parce que Hugo a demandé, papa a dit oui.
+narrateur|Hugo range la cuillère. Il sourit.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1473,6 +1500,11 @@
       <c r="AV3" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>narrateur|Hugo voit un pot inconnu. Que fait-il ?</t>
         </is>
       </c>
     </row>
@@ -1645,6 +1677,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>narrateur|Hugo a demandé. L'adulte a répondu. Le petit pot est de la compote.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1807,6 +1844,11 @@
         <v>8</v>
       </c>
       <c r="AV5" s="2" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>narrateur|Hugo boit une gorgée d'eau. Papa range le pot.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1969,6 +2011,11 @@
         <v>8</v>
       </c>
       <c r="AV6" s="2" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -1987,7 +2034,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:A3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2004,6 +2051,13 @@
       <c r="A2" t="inlineStr">
         <is>
           <t>conversion structurelle, prompts de choix alignés, TTS profilé</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-SEC.MAI.002-01.xlsx
+++ b/stories/arbres/ATOM-SEC.MAI.002-01.xlsx
@@ -844,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW6"/>
+  <dimension ref="A1:AX6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1143,6 +1143,11 @@
           <t>script</t>
         </is>
       </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1316,6 +1321,11 @@
 narrateur|Hugo range la cuillère. Il sourit.</t>
         </is>
       </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>enfants_parc</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1507,6 +1517,7 @@
           <t>narrateur|Hugo voit un pot inconnu. Que fait-il ?</t>
         </is>
       </c>
+      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1682,6 +1693,7 @@
           <t>narrateur|Hugo a demandé. L'adulte a répondu. Le petit pot est de la compote.</t>
         </is>
       </c>
+      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1849,6 +1861,7 @@
           <t>narrateur|Hugo boit une gorgée d'eau. Papa range le pot.</t>
         </is>
       </c>
+      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -2016,6 +2029,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX6" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2034,7 +2048,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:A5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2058,6 +2072,20 @@
       <c r="A3" t="inlineStr">
         <is>
           <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
         </is>
       </c>
     </row>
@@ -2072,7 +2100,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -2259,6 +2287,18 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ids de bruits (vide = silence). Le bruit se joue, puis l'histoire reprend au calme.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/stories/arbres/ATOM-SEC.MAI.002-01.xlsx
+++ b/stories/arbres/ATOM-SEC.MAI.002-01.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B30"/>
+  <dimension ref="A1:B31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -544,7 +544,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Hugo demande avant de goûter</t>
+          <t>Le petit pot d'Amir</t>
         </is>
       </c>
     </row>
@@ -830,6 +830,18 @@
       <c r="B30" t="inlineStr">
         <is>
           <t>voix-roles-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>fil_rouge</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Des pelures de poire brillent. Amir voit un petit pot fermé. Il demande à papa. C'est de la compote. Il goûte.</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1184,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Hugo est dans la cuisine. Papa coupe des poires. Un petit pot fermé est sur la table. Hugo ne le connaît pas. C'est de l'inconnu. Hugo a envie de goûter. Il va vers papa. Papa, je peux. Avant de goûter l'inconnu, il faut demander. Hugo va demander à l'adulte. Papa prend le pot. C'est de la compote. Tu peux goûter. Hugo goûte une petite cuillère. C'est doux. On demande à un adulte. Parce que Hugo a demandé, papa a dit oui. Hugo range la cuillère. Il sourit.</t>
+          <t>Des pelures de poire brillent dans l'assiette. Le jus fait un rond sur le bois. Un sac du marché pend à la chaise. La casserole chante tout bas. Ça sent le fruit tiède. Amir, tu as vu les pelures ? Oui, papa. Elles brillent. Elles brillent, comme des feuilles. Papa coupe des poires. Les morceaux tombent dans le saladier. Le saladier est blanc et froid. Tu as entendu le tic de la casserole ? Oui. Elle chante. Elle chante tout bas. En ce moment, Amir est près de la table. La table est lisse et un peu collante. Un petit pot fermé est là. Le couvercle est rond et mat. C'est quoi, papa ? Amir ne le connaît pas. C'est de l'inconnu. Amir a envie de goûter. Il pose les mains sur ses genoux. Il va vers papa. Papa, je peux ? Tu demandes. C'est bien. Avant de goûter l'inconnu, on demande. On demande à l'adulte. Papa prend le pot. C'est de la compote. Tu peux goûter. Amir prend une petite cuillère. La cuillère est froide. Il goûte une petite cuillère. C'est doux. C'est doux, papa. Oui. Parce que tu as demandé. On demande à un adulte. Bravo, Amir. Amir range la cuillère. Tu as fini de ranger la cuillère ? Oui, papa. Bravo. Tu as fait du bon travail. Le sac du marché penche encore. Les pelures brillent toujours. La casserole chante encore tout bas.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1312,13 +1324,52 @@
       <c r="AV2" s="2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>narrateur|Hugo est dans la cuisine. Papa coupe des poires. Un petit pot fermé est sur la table. Hugo ne le connaît pas. C'est de l'inconnu. Hugo a envie de goûter. Il va vers papa.
-enfant-m|Papa, je peux. Avant de goûter l'inconnu, il faut demander.
-narrateur|Hugo va demander à l'adulte. Papa prend le pot.
-papa|C'est de la compote. Tu peux goûter.
-narrateur|Hugo goûte une petite cuillère. C'est doux.
-papa|On demande à un adulte. Parce que Hugo a demandé, papa a dit oui.
-narrateur|Hugo range la cuillère. Il sourit.</t>
+          <t>narrateur|Des pelures de poire brillent dans l'assiette.
+narrateur|Le jus fait un rond sur le bois.
+narrateur|Un sac du marché pend à la chaise.
+narrateur|La casserole chante tout bas.
+narrateur|Ça sent le fruit tiède.
+papa|Amir, tu as vu les pelures ?
+enfant-m|Oui, papa. Elles brillent.
+papa|Elles brillent, comme des feuilles.
+narrateur|Papa coupe des poires.
+narrateur|Les morceaux tombent dans le saladier.
+narrateur|Le saladier est blanc et froid.
+papa|Tu as entendu le tic de la casserole ?
+enfant-m|Oui. Elle chante.
+papa|Elle chante tout bas.
+narrateur|En ce moment, Amir est près de la table.
+narrateur|La table est lisse et un peu collante.
+narrateur|Un petit pot fermé est là.
+narrateur|Le couvercle est rond et mat.
+enfant-m|C'est quoi, papa ?
+narrateur|Amir ne le connaît pas.
+narrateur|C'est de l'inconnu.
+narrateur|Amir a envie de goûter.
+narrateur|Il pose les mains sur ses genoux.
+narrateur|Il va vers papa.
+enfant-m|Papa, je peux ?
+papa|Tu demandes. C'est bien.
+narrateur|Avant de goûter l'inconnu, on demande.
+narrateur|On demande à l'adulte.
+narrateur|Papa prend le pot.
+papa|C'est de la compote.
+papa|Tu peux goûter.
+narrateur|Amir prend une petite cuillère.
+narrateur|La cuillère est froide.
+narrateur|Il goûte une petite cuillère.
+narrateur|C'est doux.
+enfant-m|C'est doux, papa.
+papa|Oui. Parce que tu as demandé.
+papa|On demande à un adulte.
+papa|Bravo, Amir.
+narrateur|Amir range la cuillère.
+papa|Tu as fini de ranger la cuillère ?
+enfant-m|Oui, papa.
+papa|Bravo. Tu as fait du bon travail.
+narrateur|Le sac du marché penche encore.
+narrateur|Les pelures brillent toujours.
+narrateur|La casserole chante encore tout bas.</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
@@ -1350,7 +1401,7 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Hugo voit un pot inconnu. Que fait-il ?</t>
+          <t>Amir voit un pot inconnu. Que fait-il ?</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
@@ -1514,10 +1565,10 @@
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>narrateur|Hugo voit un pot inconnu. Que fait-il ?</t>
-        </is>
-      </c>
-      <c r="AX3" t="inlineStr"/>
+          <t>narrateur|Amir voit un pot inconnu.
+narrateur|Que fait-il ?</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1542,7 +1593,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Hugo a demandé. L'adulte a répondu. Le petit pot est de la compote.</t>
+          <t>Amir a demandé. L'adulte a répondu. Le petit pot est de la compote. Tu as demandé à papa ? Oui. Bravo. On demande à un adulte. La cuillère est dans le tiroir. Ça sent encore les poires. Le saladier est près de l'évier. Les poires sont prêtes ? Oui, papa.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -1690,10 +1741,20 @@
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>narrateur|Hugo a demandé. L'adulte a répondu. Le petit pot est de la compote.</t>
-        </is>
-      </c>
-      <c r="AX4" t="inlineStr"/>
+          <t>narrateur|Amir a demandé.
+narrateur|L'adulte a répondu.
+narrateur|Le petit pot est de la compote.
+papa|Tu as demandé à papa ?
+enfant-m|Oui.
+papa|Bravo.
+papa|On demande à un adulte.
+narrateur|La cuillère est dans le tiroir.
+narrateur|Ça sent encore les poires.
+narrateur|Le saladier est près de l'évier.
+papa|Les poires sont prêtes ?
+enfant-m|Oui, papa.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1718,7 +1779,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Hugo boit une gorgée d'eau. Papa range le pot.</t>
+          <t>Amir boit une gorgée d'eau. L'eau est fraîche. Le pot est rangé ? Oui, papa. Bravo. Tu as fait du bon travail. Papa range le pot. Le sac du marché reste sur la chaise. Les pelures font encore un petit brillant.</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -1858,10 +1919,16 @@
       <c r="AV5" s="2" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>narrateur|Hugo boit une gorgée d'eau. Papa range le pot.</t>
-        </is>
-      </c>
-      <c r="AX5" t="inlineStr"/>
+          <t>narrateur|Amir boit une gorgée d'eau.
+narrateur|L'eau est fraîche.
+papa|Le pot est rangé ?
+enfant-m|Oui, papa.
+papa|Bravo. Tu as fait du bon travail.
+narrateur|Papa range le pot.
+narrateur|Le sac du marché reste sur la chaise.
+narrateur|Les pelures font encore un petit brillant.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1886,7 +1953,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Amir a vu un pot inconnu. Il a demandé à papa. C'était de la compote. Bravo, Amir. C'était doux. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -2026,10 +2093,14 @@
       <c r="AV6" s="2" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
-        </is>
-      </c>
-      <c r="AX6" t="inlineStr"/>
+          <t>narrateur|Amir a vu un pot inconnu.
+narrateur|Il a demandé à papa.
+narrateur|C'était de la compote.
+papa|Bravo, Amir.
+enfant-m|C'était doux.
+narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2048,7 +2119,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A5"/>
+  <dimension ref="A1:A6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2086,6 +2157,13 @@
       <c r="A5" t="inlineStr">
         <is>
           <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>F-NAR-009 ouverture du monde, fusion agents</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-SEC.MAI.002-01.xlsx
+++ b/stories/arbres/ATOM-SEC.MAI.002-01.xlsx
@@ -1184,12 +1184,12 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Des pelures de poire brillent dans l'assiette. Le jus fait un rond sur le bois. Un sac du marché pend à la chaise. La casserole chante tout bas. Ça sent le fruit tiède. Amir, tu as vu les pelures ? Oui, papa. Elles brillent. Elles brillent, comme des feuilles. Papa coupe des poires. Les morceaux tombent dans le saladier. Le saladier est blanc et froid. Tu as entendu le tic de la casserole ? Oui. Elle chante. Elle chante tout bas. En ce moment, Amir est près de la table. La table est lisse et un peu collante. Un petit pot fermé est là. Le couvercle est rond et mat. C'est quoi, papa ? Amir ne le connaît pas. C'est de l'inconnu. Amir a envie de goûter. Il pose les mains sur ses genoux. Il va vers papa. Papa, je peux ? Tu demandes. C'est bien. Avant de goûter l'inconnu, on demande. On demande à l'adulte. Papa prend le pot. C'est de la compote. Tu peux goûter. Amir prend une petite cuillère. La cuillère est froide. Il goûte une petite cuillère. C'est doux. C'est doux, papa. Oui. Parce que tu as demandé. On demande à un adulte. Bravo, Amir. Amir range la cuillère. Tu as fini de ranger la cuillère ? Oui, papa. Bravo. Tu as fait du bon travail. Le sac du marché penche encore. Les pelures brillent toujours. La casserole chante encore tout bas.</t>
+          <t>Des pelures de poire brillent dans l'assiette. Le jus fait un rond sur le bois. Un sac du marché pend à la chaise. La casserole chante tout bas. Ça sent le fruit tiède. Amir, tu as vu les pelures ? Oui, papa. Elles brillent. Elles brillent, comme des feuilles. Papa coupe des poires. Les morceaux tombent dans le saladier. Le saladier est blanc et froid. Tu as entendu le tic de la casserole ? Oui. Elle chante. Elle chante tout bas. En ce moment, Amir est près de la table. La table est lisse et un peu collante. Un petit pot fermé est là. Le couvercle est rond et mat. C'est quoi, papa ? Amir ne le connaît pas. C'est de l'inconnu. Amir a envie de goûter. Il pose les mains sur ses genoux. Il va vers papa. Papa, je peux ? Tu demandes. C'est bien. Avant de goûter l'inconnu, on demande. On demande à l'adulte. Papa prend le pot. C'est de la compote. Tu peux goûter. Amir prend une petite cuillère. La cuillère est froide. Il goûte une petite cuillère. C'est doux. C'est doux, papa. Oui. Parce que tu as demandé. On demande à un adulte. Bravo, Amir. Amir range la cuillère. Tu as fini de ranger la cuillère ? Oui, papa. Le sac du marché penche encore. Les pelures brillent toujours. La casserole chante encore tout bas.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Hugo est dans la cuisine. Papa coupe des poires. Un petit pot fermé est sur la table. Hugo ne le connaît pas. C'est de l'inconnu. Hugo a envie de goûter. Il va vers papa. Hugo dit : papa, je peux. Avant de goûter l'inconnu, il faut &lt;emphasis level="moderate"&gt;demander&lt;/emphasis&gt;. Hugo va demander à l'adulte. Papa prend le pot. Papa dit : c'est de la compote. Tu peux goûter. Hugo goûte une petite cuillère. C'est doux. Papa dit : on demande à un adulte. Parce que Hugo a demandé, papa a dit oui. Hugo range la cuillère. Il sourit.&lt;/prosody&gt;&lt;break time="400ms"/&gt;&lt;/speak&gt;</t>
+          <t>Des pelures de poire brillent dans l'assiette. Le jus fait un rond sur le bois. Un sac du marché pend à la chaise. La casserole chante tout bas. Ça sent le fruit tiède. Amir, tu as vu les pelures ? Oui, papa. Elles brillent. Elles brillent, comme des feuilles. Papa coupe des poires. Les morceaux tombent dans le saladier. Le saladier est blanc et froid. Tu as entendu le tic de la casserole ? Oui. Elle chante. Elle chante tout bas. En ce moment, Amir est près de la table. La table est lisse et un peu collante. Un petit pot fermé est là. Le couvercle est rond et mat. C'est quoi, papa ? Amir ne le connaît pas. C'est de l'inconnu. Amir a envie de goûter. Il pose les mains sur ses genoux. Il va vers papa. Papa, je peux ? Tu demandes. C'est bien. Avant de goûter l'inconnu, on demande. On demande à l'adulte. Papa prend le pot. C'est de la compote. Tu peux goûter. Amir prend une petite cuillère. La cuillère est froide. Il goûte une petite cuillère. C'est doux. C'est doux, papa. Oui. Parce que tu as demandé. On demande à un adulte. Bravo, Amir. Amir range la cuillère. Tu as fini de ranger la cuillère ? Oui, papa. Le sac du marché penche encore. Les pelures brillent toujours. La casserole chante encore tout bas.</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
@@ -1366,7 +1366,6 @@
 narrateur|Amir range la cuillère.
 papa|Tu as fini de ranger la cuillère ?
 enfant-m|Oui, papa.
-papa|Bravo. Tu as fait du bon travail.
 narrateur|Le sac du marché penche encore.
 narrateur|Les pelures brillent toujours.
 narrateur|La casserole chante encore tout bas.</t>
@@ -1406,7 +1405,7 @@
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="low"&gt;Hugo voit un pot &lt;emphasis level="moderate"&gt;inconnu&lt;/emphasis&gt;. Que fait-il ?&lt;/prosody&gt;&lt;break time="250ms"/&gt;&lt;/speak&gt;</t>
+          <t>Amir voit un pot inconnu. Que fait-il ?</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
@@ -1598,7 +1597,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="low"&gt;Hugo a demandé. L'&lt;emphasis level="moderate"&gt;adulte&lt;/emphasis&gt; a répondu. Le petit pot est de la compote.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Amir a demandé. L'adulte a répondu. Le petit pot est de la compote. Tu as demandé à papa ? Oui. Bravo. On demande à un adulte. La cuillère est dans le tiroir. Ça sent encore les poires. Le saladier est près de l'évier. Les poires sont prêtes ? Oui, papa.</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -1779,12 +1778,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Amir boit une gorgée d'eau. L'eau est fraîche. Le pot est rangé ? Oui, papa. Bravo. Tu as fait du bon travail. Papa range le pot. Le sac du marché reste sur la chaise. Les pelures font encore un petit brillant.</t>
+          <t>Amir boit une gorgée d'eau. L'eau est fraîche. Le pot est rangé ? Oui, papa. Papa range le pot. Le sac du marché reste sur la chaise. Les pelures font encore un petit brillant.</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="low"&gt;Hugo boit une gorgée d'eau. Papa range le pot.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Amir boit une gorgée d'eau. L'eau est fraîche. Le pot est rangé ? Oui, papa. Papa range le pot. Le sac du marché reste sur la chaise. Les pelures font encore un petit brillant.</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1923,7 +1922,6 @@
 narrateur|L'eau est fraîche.
 papa|Le pot est rangé ?
 enfant-m|Oui, papa.
-papa|Bravo. Tu as fait du bon travail.
 narrateur|Papa range le pot.
 narrateur|Le sac du marché reste sur la chaise.
 narrateur|Les pelures font encore un petit brillant.</t>
@@ -1953,12 +1951,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>Amir a vu un pot inconnu. Il a demandé à papa. C'était de la compote. Bravo, Amir. C'était doux. L'histoire est finie.</t>
+          <t>Amir a vu un pot inconnu. Il a demandé à papa. C'était de la compote. Bravo, Amir. C'était doux.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="low"&gt;L'histoire est finie.&lt;/prosody&gt;&lt;break time="600ms"/&gt;&lt;/speak&gt;</t>
+          <t>Amir a vu un pot inconnu. Il a demandé à papa. C'était de la compote. Bravo, Amir. C'était doux.</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -2097,8 +2095,7 @@
 narrateur|Il a demandé à papa.
 narrateur|C'était de la compote.
 papa|Bravo, Amir.
-enfant-m|C'était doux.
-narrateur|L'histoire est finie.</t>
+enfant-m|C'était doux.</t>
         </is>
       </c>
     </row>
@@ -2119,7 +2116,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A6"/>
+  <dimension ref="A1:A7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2164,6 +2161,13 @@
       <c r="A6" t="inlineStr">
         <is>
           <t>F-NAR-009 ouverture du monde, fusion agents</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>F-NAR-008 récit, pas une leçon en puces</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-SEC.MAI.002-01.xlsx
+++ b/stories/arbres/ATOM-SEC.MAI.002-01.xlsx
@@ -683,7 +683,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Hugo, papa</t>
+          <t>Amir, papa</t>
         </is>
       </c>
     </row>
